--- a/Assets/Data/Dungeon0070.xlsx
+++ b/Assets/Data/Dungeon0070.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -51,6 +51,9 @@
     <t>Mv</t>
   </si>
   <si>
+    <t>Mg</t>
+  </si>
+  <si>
     <t>DrS</t>
   </si>
   <si>
@@ -65,10 +68,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -88,32 +91,47 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -138,16 +156,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -156,44 +174,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -216,10 +196,33 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,6 +242,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -251,7 +266,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,19 +320,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,139 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,11 +436,65 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,30 +516,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -492,41 +525,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -538,145 +541,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1612,9 +1615,11 @@
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1746,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>9</v>
@@ -3675,13 +3680,13 @@
         <v>9</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>9</v>
@@ -3737,18 +3742,20 @@
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>9</v>
@@ -3811,13 +3818,13 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>9</v>
@@ -3883,7 +3890,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>9</v>
@@ -3900,7 +3907,6 @@
       <c r="M10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N10"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -3965,7 +3971,6 @@
       <c r="M11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N11"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -4098,7 +4103,6 @@
       <c r="M13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N13"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -4140,7 +4144,6 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>

--- a/Assets/Data/Dungeon0070.xlsx
+++ b/Assets/Data/Dungeon0070.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="7960" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -101,8 +101,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -121,6 +121,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -128,22 +151,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,32 +172,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -195,7 +189,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,9 +210,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,7 +233,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -243,22 +250,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,7 +273,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,73 +381,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,25 +435,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,61 +453,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,6 +464,39 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -485,43 +518,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,9 +541,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,7 +572,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,7 +581,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -590,127 +590,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5528,6 +5528,9 @@
   <sheetPr/>
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
+  <cols>
+    <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
